--- a/source_data/Fig5.xlsx
+++ b/source_data/Fig5.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Per economy: share of addressable fuel demand made at home with annual support for the cost premium capped at 1%, 2% and 3% of GDP (bars), land ceiling (5% of screened eligible land, at most 2% of territory; end caps), net import share of oil- and gas-based fuels (red ticks), share of net imports replaced, and the group of the figure; all in percent</t>
+          <t>Per economy: share of addressable fuel demand made at home with annual support for the cost premium capped at 1%, 2% and 3% of GDP (bars), land ceiling (5% of screened eligible land, at most 2% of territory; end caps), net import share of oil- and gas-based fuels (red ticks), share of net imports replaced, and the group of the figure; all in percent. Hatching is the part of the land ceiling above the 3%-of-GDP bar. no_net_trade_record = True marks the starred economies, whose tick is one minus domestic production over consumption. Sheets 2030, 2040 and 2050 are panels a, b and c</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,11 @@
           <t>imports_replaced_3pct_gdp</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>no_net_trade_record</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -560,6 +565,9 @@
       <c r="I2" t="n">
         <v>85.68000000000001</v>
       </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -589,6 +597,9 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -622,6 +633,9 @@
       <c r="I4" t="n">
         <v>69.17</v>
       </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -655,6 +669,9 @@
       <c r="I5" t="n">
         <v>4.26</v>
       </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,6 +705,9 @@
       <c r="I6" t="n">
         <v>3.15</v>
       </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -721,6 +741,9 @@
       <c r="I7" t="n">
         <v>4.11</v>
       </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -754,6 +777,9 @@
       <c r="I8" t="n">
         <v>100</v>
       </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -787,6 +813,9 @@
       <c r="I9" t="n">
         <v>100</v>
       </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -820,6 +849,9 @@
       <c r="I10" t="n">
         <v>11.94</v>
       </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -853,6 +885,9 @@
       <c r="I11" t="n">
         <v>10.13</v>
       </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -886,6 +921,9 @@
       <c r="I12" t="n">
         <v>29.03</v>
       </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -919,6 +957,9 @@
       <c r="I13" t="n">
         <v>3.13</v>
       </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -952,6 +993,9 @@
       <c r="I14" t="n">
         <v>7.81</v>
       </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -985,6 +1029,9 @@
       <c r="I15" t="n">
         <v>5.24</v>
       </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1018,6 +1065,9 @@
       <c r="I16" t="n">
         <v>28.21</v>
       </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1051,6 +1101,9 @@
       <c r="I17" t="n">
         <v>100</v>
       </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1084,6 +1137,9 @@
       <c r="I18" t="n">
         <v>100</v>
       </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1117,6 +1173,9 @@
       <c r="I19" t="n">
         <v>79.66</v>
       </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1150,6 +1209,9 @@
       <c r="I20" t="n">
         <v>43.5</v>
       </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1183,6 +1245,9 @@
       <c r="I21" t="n">
         <v>12</v>
       </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1216,6 +1281,9 @@
       <c r="I22" t="n">
         <v>3.45</v>
       </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1249,6 +1317,9 @@
       <c r="I23" t="n">
         <v>61.6</v>
       </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1282,6 +1353,9 @@
       <c r="I24" t="n">
         <v>15.2</v>
       </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,6 +1389,9 @@
       <c r="I25" t="n">
         <v>100</v>
       </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1348,6 +1425,9 @@
       <c r="I26" t="n">
         <v>68.97</v>
       </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1381,6 +1461,9 @@
       <c r="I27" t="n">
         <v>100</v>
       </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1410,6 +1493,9 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1443,6 +1529,9 @@
       <c r="I29" t="n">
         <v>91.34</v>
       </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1472,6 +1561,9 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1501,6 +1593,9 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1513,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,6 +1657,11 @@
           <t>imports_replaced_3pct_gdp</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>no_net_trade_record</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1595,6 +1695,9 @@
       <c r="I2" t="n">
         <v>96.84999999999999</v>
       </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1624,6 +1727,9 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1657,6 +1763,9 @@
       <c r="I4" t="n">
         <v>80.26000000000001</v>
       </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1690,6 +1799,9 @@
       <c r="I5" t="n">
         <v>5.17</v>
       </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1723,6 +1835,9 @@
       <c r="I6" t="n">
         <v>3.46</v>
       </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1756,6 +1871,9 @@
       <c r="I7" t="n">
         <v>4.23</v>
       </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1789,6 +1907,9 @@
       <c r="I8" t="n">
         <v>100</v>
       </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1822,6 +1943,9 @@
       <c r="I9" t="n">
         <v>100</v>
       </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1855,6 +1979,9 @@
       <c r="I10" t="n">
         <v>13.12</v>
       </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1888,6 +2015,9 @@
       <c r="I11" t="n">
         <v>14.05</v>
       </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1921,6 +2051,9 @@
       <c r="I12" t="n">
         <v>29.99</v>
       </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1954,6 +2087,9 @@
       <c r="I13" t="n">
         <v>3.36</v>
       </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1987,6 +2123,9 @@
       <c r="I14" t="n">
         <v>8.82</v>
       </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2020,6 +2159,9 @@
       <c r="I15" t="n">
         <v>5.91</v>
       </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2053,6 +2195,9 @@
       <c r="I16" t="n">
         <v>31.61</v>
       </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2086,6 +2231,9 @@
       <c r="I17" t="n">
         <v>100</v>
       </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2119,6 +2267,9 @@
       <c r="I18" t="n">
         <v>100</v>
       </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2152,6 +2303,9 @@
       <c r="I19" t="n">
         <v>100</v>
       </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2185,6 +2339,9 @@
       <c r="I20" t="n">
         <v>45.93</v>
       </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2218,6 +2375,9 @@
       <c r="I21" t="n">
         <v>16.46</v>
       </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2251,6 +2411,9 @@
       <c r="I22" t="n">
         <v>4.03</v>
       </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2284,6 +2447,9 @@
       <c r="I23" t="n">
         <v>83.63</v>
       </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2317,6 +2483,9 @@
       <c r="I24" t="n">
         <v>16.53</v>
       </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2350,6 +2519,9 @@
       <c r="I25" t="n">
         <v>100</v>
       </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2383,6 +2555,9 @@
       <c r="I26" t="n">
         <v>100</v>
       </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2416,6 +2591,9 @@
       <c r="I27" t="n">
         <v>100</v>
       </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2445,6 +2623,9 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2478,6 +2659,9 @@
       <c r="I29" t="n">
         <v>100</v>
       </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2507,6 +2691,9 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2536,6 +2723,9 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2548,7 +2738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2597,6 +2787,11 @@
           <t>imports_replaced_3pct_gdp</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>no_net_trade_record</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2630,6 +2825,9 @@
       <c r="I2" t="n">
         <v>100</v>
       </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2659,6 +2857,9 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2692,6 +2893,9 @@
       <c r="I4" t="n">
         <v>87.68000000000001</v>
       </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2725,6 +2929,9 @@
       <c r="I5" t="n">
         <v>5.88</v>
       </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2758,6 +2965,9 @@
       <c r="I6" t="n">
         <v>3.86</v>
       </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2791,6 +3001,9 @@
       <c r="I7" t="n">
         <v>4.66</v>
       </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2824,6 +3037,9 @@
       <c r="I8" t="n">
         <v>100</v>
       </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2857,6 +3073,9 @@
       <c r="I9" t="n">
         <v>100</v>
       </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2890,6 +3109,9 @@
       <c r="I10" t="n">
         <v>14.5</v>
       </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2923,6 +3145,9 @@
       <c r="I11" t="n">
         <v>16.37</v>
       </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2956,6 +3181,9 @@
       <c r="I12" t="n">
         <v>32.89</v>
       </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2989,6 +3217,9 @@
       <c r="I13" t="n">
         <v>3.58</v>
       </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3022,6 +3253,9 @@
       <c r="I14" t="n">
         <v>9.81</v>
       </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3055,6 +3289,9 @@
       <c r="I15" t="n">
         <v>6.41</v>
       </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3088,6 +3325,9 @@
       <c r="I16" t="n">
         <v>35.2</v>
       </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3121,6 +3361,9 @@
       <c r="I17" t="n">
         <v>100</v>
       </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3154,6 +3397,9 @@
       <c r="I18" t="n">
         <v>100</v>
       </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3187,6 +3433,9 @@
       <c r="I19" t="n">
         <v>100</v>
       </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3220,6 +3469,9 @@
       <c r="I20" t="n">
         <v>50.72</v>
       </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3253,6 +3505,9 @@
       <c r="I21" t="n">
         <v>20.98</v>
       </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3286,6 +3541,9 @@
       <c r="I22" t="n">
         <v>5.19</v>
       </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3319,6 +3577,9 @@
       <c r="I23" t="n">
         <v>100</v>
       </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3352,6 +3613,9 @@
       <c r="I24" t="n">
         <v>17.77</v>
       </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3385,6 +3649,9 @@
       <c r="I25" t="n">
         <v>100</v>
       </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3418,6 +3685,9 @@
       <c r="I26" t="n">
         <v>100</v>
       </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3451,6 +3721,9 @@
       <c r="I27" t="n">
         <v>100</v>
       </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3480,6 +3753,9 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3513,6 +3789,9 @@
       <c r="I29" t="n">
         <v>100</v>
       </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3542,6 +3821,9 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3571,6 +3853,9 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/source_data/Fig5.xlsx
+++ b/source_data/Fig5.xlsx
@@ -545,25 +545,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>54.56</v>
+        <v>54.55</v>
       </c>
       <c r="D2" t="n">
-        <v>54.56</v>
+        <v>54.55</v>
       </c>
       <c r="E2" t="n">
-        <v>54.56</v>
+        <v>54.55</v>
       </c>
       <c r="F2" t="n">
-        <v>54.56</v>
+        <v>54.55</v>
       </c>
       <c r="G2" t="n">
-        <v>61.17</v>
+        <v>61.16</v>
       </c>
       <c r="H2" t="n">
-        <v>85.68000000000001</v>
+        <v>85.66</v>
       </c>
       <c r="I2" t="n">
-        <v>85.68000000000001</v>
+        <v>85.66</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -613,25 +613,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>54.86</v>
+        <v>54.83</v>
       </c>
       <c r="D4" t="n">
-        <v>54.86</v>
+        <v>54.83</v>
       </c>
       <c r="E4" t="n">
-        <v>54.86</v>
+        <v>54.83</v>
       </c>
       <c r="F4" t="n">
-        <v>54.86</v>
+        <v>54.83</v>
       </c>
       <c r="G4" t="n">
-        <v>76.97</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>69.17</v>
+        <v>69.14</v>
       </c>
       <c r="I4" t="n">
-        <v>69.17</v>
+        <v>69.14</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -685,16 +685,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="D6" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="E6" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="F6" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="G6" t="n">
         <v>96.7</v>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>45.01</v>
+        <v>45.02</v>
       </c>
       <c r="D8" t="n">
-        <v>73.94</v>
+        <v>73.95</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
@@ -799,13 +799,13 @@
         <v>50.5</v>
       </c>
       <c r="E9" t="n">
-        <v>69.27</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>70.26000000000001</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>46.43</v>
+        <v>46.42</v>
       </c>
       <c r="H9" t="n">
         <v>57.72</v>
@@ -913,7 +913,7 @@
         <v>24.8</v>
       </c>
       <c r="G12" t="n">
-        <v>83.93000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="H12" t="n">
         <v>29.03</v>
@@ -1057,7 +1057,7 @@
         <v>18.35</v>
       </c>
       <c r="G16" t="n">
-        <v>66.93000000000001</v>
+        <v>66.92</v>
       </c>
       <c r="H16" t="n">
         <v>28.21</v>
@@ -1096,7 +1096,7 @@
         <v>18.59</v>
       </c>
       <c r="H17" t="n">
-        <v>82.76000000000001</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>100</v>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28.39</v>
+        <v>28.4</v>
       </c>
       <c r="D18" t="n">
-        <v>44.68</v>
+        <v>44.69</v>
       </c>
       <c r="E18" t="n">
-        <v>60.12</v>
+        <v>60.13</v>
       </c>
       <c r="F18" t="n">
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>53.93</v>
+        <v>53.92</v>
       </c>
       <c r="H18" t="n">
         <v>48.83</v>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>31.02</v>
+        <v>31.03</v>
       </c>
       <c r="D19" t="n">
         <v>55.59</v>
       </c>
       <c r="E19" t="n">
-        <v>79.66</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="F19" t="n">
         <v>100</v>
@@ -1168,10 +1168,10 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>31.02</v>
+        <v>31.03</v>
       </c>
       <c r="I19" t="n">
-        <v>79.66</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>66.28</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="D25" t="n">
         <v>100</v>
@@ -1381,7 +1381,7 @@
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>96.31999999999999</v>
+        <v>96.31</v>
       </c>
       <c r="H25" t="n">
         <v>68.29000000000001</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>66.84999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="D27" t="n">
         <v>100</v>
@@ -1453,7 +1453,7 @@
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>56.69</v>
+        <v>56.67</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>39.83</v>
+        <v>39.84</v>
       </c>
       <c r="D29" t="n">
-        <v>65.67</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>90.42</v>
+        <v>90.41</v>
       </c>
       <c r="F29" t="n">
         <v>100</v>
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>41.74</v>
+        <v>43.14</v>
       </c>
       <c r="D30" t="n">
-        <v>41.74</v>
+        <v>43.76</v>
       </c>
       <c r="E30" t="n">
-        <v>41.74</v>
+        <v>43.76</v>
       </c>
       <c r="F30" t="n">
-        <v>41.74</v>
+        <v>43.76</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1675,25 +1675,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.11</v>
+        <v>57.1</v>
       </c>
       <c r="D2" t="n">
-        <v>57.11</v>
+        <v>57.1</v>
       </c>
       <c r="E2" t="n">
-        <v>57.11</v>
+        <v>57.1</v>
       </c>
       <c r="F2" t="n">
-        <v>57.11</v>
+        <v>57.1</v>
       </c>
       <c r="G2" t="n">
-        <v>61.17</v>
+        <v>61.16</v>
       </c>
       <c r="H2" t="n">
-        <v>96.84999999999999</v>
+        <v>96.83</v>
       </c>
       <c r="I2" t="n">
-        <v>96.84999999999999</v>
+        <v>96.83</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -1743,25 +1743,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63.4</v>
+        <v>63.37</v>
       </c>
       <c r="D4" t="n">
-        <v>63.4</v>
+        <v>63.37</v>
       </c>
       <c r="E4" t="n">
-        <v>63.4</v>
+        <v>63.37</v>
       </c>
       <c r="F4" t="n">
-        <v>63.4</v>
+        <v>63.37</v>
       </c>
       <c r="G4" t="n">
-        <v>76.97</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>80.26000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="I4" t="n">
-        <v>80.26000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>65.64</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>100</v>
@@ -1923,19 +1923,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41.95</v>
+        <v>41.96</v>
       </c>
       <c r="D9" t="n">
-        <v>72.29000000000001</v>
+        <v>72.28</v>
       </c>
       <c r="E9" t="n">
-        <v>73.12</v>
+        <v>73.11</v>
       </c>
       <c r="F9" t="n">
-        <v>73.12</v>
+        <v>73.11</v>
       </c>
       <c r="G9" t="n">
-        <v>46.43</v>
+        <v>46.42</v>
       </c>
       <c r="H9" t="n">
         <v>82.66</v>
@@ -2043,7 +2043,7 @@
         <v>25.61</v>
       </c>
       <c r="G12" t="n">
-        <v>83.93000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="H12" t="n">
         <v>29.99</v>
@@ -2103,16 +2103,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.01</v>
+        <v>8.02</v>
       </c>
       <c r="D14" t="n">
-        <v>8.01</v>
+        <v>8.02</v>
       </c>
       <c r="E14" t="n">
-        <v>8.01</v>
+        <v>8.02</v>
       </c>
       <c r="F14" t="n">
-        <v>8.01</v>
+        <v>8.02</v>
       </c>
       <c r="G14" t="n">
         <v>92.68000000000001</v>
@@ -2139,16 +2139,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D15" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="E15" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="F15" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="G15" t="n">
         <v>52.01</v>
@@ -2175,19 +2175,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.63</v>
+        <v>20.62</v>
       </c>
       <c r="D16" t="n">
-        <v>20.63</v>
+        <v>20.62</v>
       </c>
       <c r="E16" t="n">
-        <v>20.63</v>
+        <v>20.62</v>
       </c>
       <c r="F16" t="n">
-        <v>20.63</v>
+        <v>20.62</v>
       </c>
       <c r="G16" t="n">
-        <v>66.93000000000001</v>
+        <v>66.92</v>
       </c>
       <c r="H16" t="n">
         <v>31.61</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>39.42</v>
+        <v>39.45</v>
       </c>
       <c r="D18" t="n">
-        <v>61.83</v>
+        <v>61.85</v>
       </c>
       <c r="E18" t="n">
         <v>82.94</v>
@@ -2259,10 +2259,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>53.93</v>
+        <v>53.92</v>
       </c>
       <c r="H18" t="n">
-        <v>67.25</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="I18" t="n">
         <v>100</v>
@@ -2286,7 +2286,7 @@
         <v>44.56</v>
       </c>
       <c r="D19" t="n">
-        <v>82.34999999999999</v>
+        <v>82.34</v>
       </c>
       <c r="E19" t="n">
         <v>100</v>
@@ -2319,16 +2319,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>43.48</v>
+        <v>43.47</v>
       </c>
       <c r="D20" t="n">
-        <v>43.48</v>
+        <v>43.47</v>
       </c>
       <c r="E20" t="n">
-        <v>43.48</v>
+        <v>43.47</v>
       </c>
       <c r="F20" t="n">
-        <v>43.48</v>
+        <v>43.47</v>
       </c>
       <c r="G20" t="n">
         <v>94.17</v>
@@ -2370,10 +2370,10 @@
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>16.46</v>
+        <v>16.45</v>
       </c>
       <c r="I21" t="n">
-        <v>16.46</v>
+        <v>16.45</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>31.97</v>
+        <v>31.98</v>
       </c>
       <c r="D23" t="n">
         <v>60.6</v>
       </c>
       <c r="E23" t="n">
-        <v>83.56</v>
+        <v>83.55</v>
       </c>
       <c r="F23" t="n">
         <v>100</v>
@@ -2442,7 +2442,7 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="I23" t="n">
         <v>83.63</v>
@@ -2511,7 +2511,7 @@
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>96.31999999999999</v>
+        <v>96.31</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>42.75</v>
+        <v>42.76</v>
       </c>
       <c r="D26" t="n">
         <v>73.95999999999999</v>
@@ -2550,7 +2550,7 @@
         <v>99.90000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>42.86</v>
+        <v>42.87</v>
       </c>
       <c r="I26" t="n">
         <v>100</v>
@@ -2583,7 +2583,7 @@
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>56.69</v>
+        <v>56.67</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
@@ -2607,16 +2607,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>65.34</v>
+        <v>65.33</v>
       </c>
       <c r="D28" t="n">
-        <v>65.34</v>
+        <v>65.33</v>
       </c>
       <c r="E28" t="n">
-        <v>65.34</v>
+        <v>65.33</v>
       </c>
       <c r="F28" t="n">
-        <v>65.34</v>
+        <v>65.33</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>58.62</v>
+        <v>58.63</v>
       </c>
       <c r="D29" t="n">
         <v>100</v>
@@ -2654,7 +2654,7 @@
         <v>99.12</v>
       </c>
       <c r="H29" t="n">
-        <v>59.16</v>
+        <v>59.17</v>
       </c>
       <c r="I29" t="n">
         <v>100</v>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>49.03</v>
+        <v>51.45</v>
       </c>
       <c r="D30" t="n">
-        <v>49.03</v>
+        <v>51.45</v>
       </c>
       <c r="E30" t="n">
-        <v>49.03</v>
+        <v>51.45</v>
       </c>
       <c r="F30" t="n">
-        <v>49.03</v>
+        <v>51.45</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2805,19 +2805,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66.51000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="D2" t="n">
-        <v>66.51000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="E2" t="n">
-        <v>66.51000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="F2" t="n">
-        <v>66.51000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="G2" t="n">
-        <v>61.17</v>
+        <v>61.16</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
@@ -2873,25 +2873,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>68.13</v>
+        <v>68.09</v>
       </c>
       <c r="D4" t="n">
-        <v>68.13</v>
+        <v>68.09</v>
       </c>
       <c r="E4" t="n">
-        <v>68.13</v>
+        <v>68.09</v>
       </c>
       <c r="F4" t="n">
-        <v>68.13</v>
+        <v>68.09</v>
       </c>
       <c r="G4" t="n">
-        <v>76.97</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>87.68000000000001</v>
+        <v>87.64</v>
       </c>
       <c r="I4" t="n">
-        <v>87.68000000000001</v>
+        <v>87.64</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -2981,16 +2981,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="D7" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="E7" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="F7" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="G7" t="n">
         <v>99.92</v>
@@ -3053,19 +3053,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>65.2</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>79.53</v>
+        <v>79.52</v>
       </c>
       <c r="E9" t="n">
-        <v>79.53</v>
+        <v>79.52</v>
       </c>
       <c r="F9" t="n">
-        <v>79.53</v>
+        <v>79.52</v>
       </c>
       <c r="G9" t="n">
-        <v>46.43</v>
+        <v>46.42</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -3173,7 +3173,7 @@
         <v>27.44</v>
       </c>
       <c r="G12" t="n">
-        <v>83.93000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="H12" t="n">
         <v>32.89</v>
@@ -3305,19 +3305,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.03</v>
+        <v>23.02</v>
       </c>
       <c r="D16" t="n">
-        <v>23.03</v>
+        <v>23.02</v>
       </c>
       <c r="E16" t="n">
-        <v>23.03</v>
+        <v>23.02</v>
       </c>
       <c r="F16" t="n">
-        <v>23.03</v>
+        <v>23.02</v>
       </c>
       <c r="G16" t="n">
-        <v>66.93000000000001</v>
+        <v>66.92</v>
       </c>
       <c r="H16" t="n">
         <v>35.2</v>
@@ -3341,13 +3341,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>39.52</v>
+        <v>39.53</v>
       </c>
       <c r="D17" t="n">
         <v>68.56</v>
       </c>
       <c r="E17" t="n">
-        <v>91.56</v>
+        <v>91.55</v>
       </c>
       <c r="F17" t="n">
         <v>100</v>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>56.62</v>
+        <v>56.65</v>
       </c>
       <c r="D18" t="n">
-        <v>91.44</v>
+        <v>91.45</v>
       </c>
       <c r="E18" t="n">
         <v>100</v>
@@ -3389,7 +3389,7 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>53.93</v>
+        <v>53.92</v>
       </c>
       <c r="H18" t="n">
         <v>98.76000000000001</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>71.06</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="D19" t="n">
         <v>100</v>
@@ -3428,7 +3428,7 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>71.06</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>100</v>
@@ -3641,7 +3641,7 @@
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>96.31999999999999</v>
+        <v>96.31</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -3713,7 +3713,7 @@
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>56.69</v>
+        <v>56.67</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
@@ -3805,16 +3805,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60.18</v>
+        <v>63.21</v>
       </c>
       <c r="D30" t="n">
-        <v>60.18</v>
+        <v>63.21</v>
       </c>
       <c r="E30" t="n">
-        <v>60.18</v>
+        <v>63.21</v>
       </c>
       <c r="F30" t="n">
-        <v>60.18</v>
+        <v>63.21</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
